--- a/paper/Tables/SS.xlsx
+++ b/paper/Tables/SS.xlsx
@@ -1,28 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xps-seira\Dropbox\Apps\ShareLaTeX\information_settlement\Paper\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\isaac\Dropbox\ReplicationFinal\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5DD12C-6AB0-4E03-A416-3B51BEC4A949}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E480DA9-5DCD-48F8-909B-20C8A2B1178E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24795" yWindow="-5565" windowWidth="21600" windowHeight="11175" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="PanelA" sheetId="1" r:id="rId1"/>
     <sheet name="PanelB" sheetId="4" r:id="rId2"/>
     <sheet name="SS" sheetId="6" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="447">
   <si>
     <t>Obs</t>
   </si>
@@ -56,12 +60,143 @@
     <t>Data: Pilot</t>
   </si>
   <si>
-    <t>[0, 1]</t>
+    <t>Win</t>
+  </si>
+  <si>
+    <t>Public Lawyer</t>
+  </si>
+  <si>
+    <t>Daily wage</t>
+  </si>
+  <si>
+    <t>Weekly hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conciliation </t>
+  </si>
+  <si>
+    <t>Data: Subcourt 7</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>At will worker</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>Data: ScaleUp</t>
+  </si>
+  <si>
+    <t>Panel B: Basic Variables</t>
+  </si>
+  <si>
+    <t>HD</t>
+  </si>
+  <si>
+    <t>HD Subcourt 7</t>
+  </si>
+  <si>
+    <t>Tenure (years)</t>
+  </si>
+  <si>
+    <t>Phase 1</t>
+  </si>
+  <si>
+    <t>Phase 2</t>
+  </si>
+  <si>
+    <t>Duration (years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Losing court ruling </t>
+  </si>
+  <si>
+    <t>Winning court ruling</t>
+  </si>
+  <si>
+    <t>Data: P3</t>
+  </si>
+  <si>
+    <t>Phase 3</t>
+  </si>
+  <si>
+    <t>Amount won
+(thousand pesos)</t>
+  </si>
+  <si>
+    <t>Total asked
+(thousand pesos)</t>
+  </si>
+  <si>
+    <t>.65</t>
   </si>
   <si>
     <t>(.48)</t>
   </si>
   <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>23.92</t>
+  </si>
+  <si>
+    <t>(56.3)</t>
+  </si>
+  <si>
+    <t>[0, 422.9779968261719]</t>
+  </si>
+  <si>
+    <t>343.06</t>
+  </si>
+  <si>
+    <t>(655.17)</t>
+  </si>
+  <si>
+    <t>[0, 4488.7158203125]</t>
+  </si>
+  <si>
+    <t>.63</t>
+  </si>
+  <si>
+    <t>(.48)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.07</t>
+  </si>
+  <si>
+    <t>(.25)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.02</t>
+  </si>
+  <si>
+    <t>(.14)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>duracion</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
+    <t>(.96)</t>
+  </si>
+  <si>
+    <t>[.0054794522002339, 4.960000038146973]</t>
+  </si>
+  <si>
     <t>abogado_pub</t>
   </si>
   <si>
@@ -71,6 +206,9 @@
     <t>(.3)</t>
   </si>
   <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
     <t>gen</t>
   </si>
   <si>
@@ -80,6 +218,9 @@
     <t>(.5)</t>
   </si>
   <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
     <t>trabajador_base</t>
   </si>
   <si>
@@ -89,6 +230,9 @@
     <t>(.25)</t>
   </si>
   <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
     <t>c_antiguedad</t>
   </si>
   <si>
@@ -104,6 +248,15 @@
     <t>salario_diario</t>
   </si>
   <si>
+    <t>470.05</t>
+  </si>
+  <si>
+    <t>(1100.8)</t>
+  </si>
+  <si>
+    <t>[3.33, 47526.54]</t>
+  </si>
+  <si>
     <t>horas_sem</t>
   </si>
   <si>
@@ -116,22 +269,739 @@
     <t>[3, 147]</t>
   </si>
   <si>
+    <t>.6900000000000001</t>
+  </si>
+  <si>
+    <t>(.46)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>20.36</t>
+  </si>
+  <si>
+    <t>(47.49)</t>
+  </si>
+  <si>
+    <t>[0, 422.9779968261719]</t>
+  </si>
+  <si>
+    <t>301.57</t>
+  </si>
+  <si>
+    <t>(551.15)</t>
+  </si>
+  <si>
+    <t>[6.805358409881592, 4488.7158203125]</t>
+  </si>
+  <si>
+    <t>.67</t>
+  </si>
+  <si>
+    <t>(.47)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.01</t>
+  </si>
+  <si>
+    <t>(.1)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.02</t>
+  </si>
+  <si>
+    <t>(.12)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
     <t>.98</t>
   </si>
   <si>
+    <t>(.71)</t>
+  </si>
+  <si>
+    <t>[.0054794522002339, 4.290410995483398]</t>
+  </si>
+  <si>
+    <t>.15</t>
+  </si>
+  <si>
+    <t>(.36)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.35</t>
+  </si>
+  <si>
+    <t>(.48)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.06</t>
+  </si>
+  <si>
+    <t>(.23)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>3.72</t>
+  </si>
+  <si>
+    <t>(4.72)</t>
+  </si>
+  <si>
+    <t>[.002739726100117, 25.51000022888184]</t>
+  </si>
+  <si>
+    <t>455.49</t>
+  </si>
+  <si>
+    <t>(656.22)</t>
+  </si>
+  <si>
+    <t>[21.42, 11284.789]</t>
+  </si>
+  <si>
+    <t>57.36</t>
+  </si>
+  <si>
+    <t>(15.57)</t>
+  </si>
+  <si>
+    <t>[7, 147]</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>598.3200000000001</t>
+  </si>
+  <si>
+    <t>(1438.49)</t>
+  </si>
+  <si>
+    <t>[0, 18704.697265625]</t>
+  </si>
+  <si>
+    <t>.22</t>
+  </si>
+  <si>
+    <t>(.41)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>.11</t>
+  </si>
+  <si>
+    <t>(.32)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.42</t>
+  </si>
+  <si>
+    <t>(.49)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.18</t>
+  </si>
+  <si>
+    <t>(.39)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>4.71</t>
+  </si>
+  <si>
+    <t>(6)</t>
+  </si>
+  <si>
+    <t>[.0219178088009357, 49.47123336791992]</t>
+  </si>
+  <si>
+    <t>739.84</t>
+  </si>
+  <si>
+    <t>(1360.94)</t>
+  </si>
+  <si>
+    <t>[30, 16080.0153333333]</t>
+  </si>
+  <si>
+    <t>57.31</t>
+  </si>
+  <si>
+    <t>(16.82)</t>
+  </si>
+  <si>
+    <t>[7, 258]</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>644.0600000000001</t>
+  </si>
+  <si>
+    <t>(3860.99)</t>
+  </si>
+  <si>
+    <t>[0, 100850.5390625]</t>
+  </si>
+  <si>
+    <t>.2</t>
+  </si>
+  <si>
+    <t>(.4)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>.06</t>
+  </si>
+  <si>
+    <t>(.24)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.46</t>
+  </si>
+  <si>
+    <t>(.5)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.08</t>
+  </si>
+  <si>
+    <t>(.27)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>4.33</t>
+  </si>
+  <si>
+    <t>(5.74)</t>
+  </si>
+  <si>
+    <t>[.0164383556693792, 60.60821914672852]</t>
+  </si>
+  <si>
+    <t>605.3000000000001</t>
+  </si>
+  <si>
+    <t>(1007.75)</t>
+  </si>
+  <si>
+    <t>[50, 19719.359375]</t>
+  </si>
+  <si>
+    <t>56.15</t>
+  </si>
+  <si>
+    <t>(13.38)</t>
+  </si>
+  <si>
+    <t>[6, 122.5]</t>
+  </si>
+  <si>
+    <t>win</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>liq_total</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>c_total</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>con</t>
+  </si>
+  <si>
+    <t>.42</t>
+  </si>
+  <si>
+    <t>(.49)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>cr_0</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>cr_m</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>.47</t>
+  </si>
+  <si>
+    <t>(.5)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.45</t>
+  </si>
+  <si>
+    <t>(.5)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>3.71</t>
+  </si>
+  <si>
+    <t>(4.74)</t>
+  </si>
+  <si>
+    <t>[.0082191778346896, 41.33424758911133]</t>
+  </si>
+  <si>
+    <t>323.1</t>
+  </si>
+  <si>
+    <t>(634.99)</t>
+  </si>
+  <si>
+    <t>[36.66666793823242, 18200]</t>
+  </si>
+  <si>
+    <t>52.88</t>
+  </si>
+  <si>
+    <t>(15.52)</t>
+  </si>
+  <si>
+    <t>[0, 168]</t>
+  </si>
+  <si>
+    <t>win</t>
+  </si>
+  <si>
+    <t>.65</t>
+  </si>
+  <si>
+    <t>(.48)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>liq_total</t>
+  </si>
+  <si>
+    <t>23.92</t>
+  </si>
+  <si>
+    <t>(56.3)</t>
+  </si>
+  <si>
+    <t>[0, 422.9779968261719]</t>
+  </si>
+  <si>
+    <t>c_total</t>
+  </si>
+  <si>
+    <t>343.06</t>
+  </si>
+  <si>
+    <t>(655.17)</t>
+  </si>
+  <si>
+    <t>[0, 4488.7158203125]</t>
+  </si>
+  <si>
+    <t>con</t>
+  </si>
+  <si>
+    <t>.63</t>
+  </si>
+  <si>
+    <t>(.48)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>cr_0</t>
+  </si>
+  <si>
+    <t>.07</t>
+  </si>
+  <si>
+    <t>(.25)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>cr_m</t>
+  </si>
+  <si>
+    <t>.02</t>
+  </si>
+  <si>
+    <t>(.14)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>duracion</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
+    <t>(.96)</t>
+  </si>
+  <si>
+    <t>[.0054794522002339, 4.960000038146973]</t>
+  </si>
+  <si>
+    <t>abogado_pub</t>
+  </si>
+  <si>
+    <t>.1</t>
+  </si>
+  <si>
+    <t>(.3)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>gen</t>
+  </si>
+  <si>
+    <t>.48</t>
+  </si>
+  <si>
+    <t>(.5)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>trabajador_base</t>
+  </si>
+  <si>
+    <t>.07</t>
+  </si>
+  <si>
+    <t>(.25)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>c_antiguedad</t>
+  </si>
+  <si>
+    <t>4.17</t>
+  </si>
+  <si>
+    <t>(4.99)</t>
+  </si>
+  <si>
+    <t>[0, 25.51000022888184]</t>
+  </si>
+  <si>
+    <t>salario_diario</t>
+  </si>
+  <si>
+    <t>470.05</t>
+  </si>
+  <si>
+    <t>(1100.8)</t>
+  </si>
+  <si>
+    <t>[3.33, 47526.54]</t>
+  </si>
+  <si>
+    <t>horas_sem</t>
+  </si>
+  <si>
+    <t>57.33</t>
+  </si>
+  <si>
+    <t>(15.47)</t>
+  </si>
+  <si>
+    <t>[3, 147]</t>
+  </si>
+  <si>
+    <t>.6900000000000001</t>
+  </si>
+  <si>
     <t>(.46)</t>
   </si>
   <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>20.36</t>
+  </si>
+  <si>
+    <t>(47.49)</t>
+  </si>
+  <si>
+    <t>[0, 422.9779968261719]</t>
+  </si>
+  <si>
+    <t>301.57</t>
+  </si>
+  <si>
+    <t>(551.15)</t>
+  </si>
+  <si>
+    <t>[6.805358409881592, 4488.7158203125]</t>
+  </si>
+  <si>
+    <t>.67</t>
+  </si>
+  <si>
     <t>(.47)</t>
   </si>
   <si>
-    <t>470.05</t>
-  </si>
-  <si>
-    <t>(1100.8)</t>
-  </si>
-  <si>
-    <t>[3.33, 47526.54]</t>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.01</t>
+  </si>
+  <si>
+    <t>(.1)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.02</t>
+  </si>
+  <si>
+    <t>(.12)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.98</t>
+  </si>
+  <si>
+    <t>(.71)</t>
+  </si>
+  <si>
+    <t>[.0054794522002339, 4.290410995483398]</t>
+  </si>
+  <si>
+    <t>.15</t>
+  </si>
+  <si>
+    <t>(.36)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.35</t>
+  </si>
+  <si>
+    <t>(.48)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.06</t>
+  </si>
+  <si>
+    <t>(.23)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>3.72</t>
+  </si>
+  <si>
+    <t>(4.72)</t>
+  </si>
+  <si>
+    <t>[.002739726100117, 25.51000022888184]</t>
+  </si>
+  <si>
+    <t>455.49</t>
+  </si>
+  <si>
+    <t>(656.22)</t>
+  </si>
+  <si>
+    <t>[21.42, 11284.789]</t>
+  </si>
+  <si>
+    <t>57.36</t>
+  </si>
+  <si>
+    <t>(15.57)</t>
+  </si>
+  <si>
+    <t>[7, 147]</t>
+  </si>
+  <si>
+    <t>win</t>
   </si>
   <si>
     <t>.</t>
@@ -143,311 +1013,377 @@
     <t>[, ]</t>
   </si>
   <si>
+    <t>liq_total</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>c_total</t>
+  </si>
+  <si>
+    <t>598.3200000000001</t>
+  </si>
+  <si>
+    <t>(1438.49)</t>
+  </si>
+  <si>
+    <t>[0, 18704.697265625]</t>
+  </si>
+  <si>
+    <t>con</t>
+  </si>
+  <si>
+    <t>.22</t>
+  </si>
+  <si>
+    <t>(.41)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>cr_0</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>cr_m</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>.11</t>
+  </si>
+  <si>
+    <t>(.32)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.42</t>
+  </si>
+  <si>
     <t>(.49)</t>
   </si>
   <si>
-    <t>[30, 31433.06]</t>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.18</t>
+  </si>
+  <si>
+    <t>(.39)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>4.71</t>
+  </si>
+  <si>
+    <t>(6)</t>
+  </si>
+  <si>
+    <t>[.0219178088009357, 49.47123336791992]</t>
+  </si>
+  <si>
+    <t>739.84</t>
+  </si>
+  <si>
+    <t>(1360.94)</t>
+  </si>
+  <si>
+    <t>[30, 16080.0153333333]</t>
+  </si>
+  <si>
+    <t>57.31</t>
+  </si>
+  <si>
+    <t>(16.82)</t>
   </si>
   <si>
     <t>[7, 258]</t>
   </si>
   <si>
-    <t>(.23)</t>
-  </si>
-  <si>
     <t>win</t>
   </si>
   <si>
-    <t>.65</t>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>liq_total_tope</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
   </si>
   <si>
     <t>c_total</t>
   </si>
   <si>
-    <t>343059.79</t>
-  </si>
-  <si>
-    <t>(655168.15)</t>
-  </si>
-  <si>
-    <t>[0, 4488716]</t>
-  </si>
-  <si>
-    <t>[0, 18704698]</t>
-  </si>
-  <si>
-    <t>Win</t>
-  </si>
-  <si>
-    <t>Amount won</t>
-  </si>
-  <si>
-    <t>Public Lawyer</t>
-  </si>
-  <si>
-    <t>Daily wage</t>
-  </si>
-  <si>
-    <t>Weekly hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conciliation </t>
+    <t>644.0600000000001</t>
+  </si>
+  <si>
+    <t>(3860.99)</t>
+  </si>
+  <si>
+    <t>[0, 100850.5390625]</t>
   </si>
   <si>
     <t>con</t>
   </si>
   <si>
-    <t>.63</t>
-  </si>
-  <si>
-    <t>.01</t>
-  </si>
-  <si>
-    <t>duracion</t>
-  </si>
-  <si>
-    <t>1.02</t>
-  </si>
-  <si>
-    <t>(.96)</t>
-  </si>
-  <si>
-    <t>[.0054794522002339, 4.960000038146973]</t>
-  </si>
-  <si>
-    <t>Data: Subcourt 7</t>
-  </si>
-  <si>
-    <t>.6900000000000001</t>
-  </si>
-  <si>
-    <t>301565.69</t>
-  </si>
-  <si>
-    <t>(551154.03)</t>
-  </si>
-  <si>
-    <t>[6805.3583984375, 4488716]</t>
-  </si>
-  <si>
-    <t>(.71)</t>
-  </si>
-  <si>
-    <t>[.0054794522002339, 4.290410995483398]</t>
-  </si>
-  <si>
-    <t>.15</t>
-  </si>
-  <si>
-    <t>(.36)</t>
-  </si>
-  <si>
-    <t>.35</t>
+    <t>.2</t>
+  </si>
+  <si>
+    <t>(.4)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>cr_0</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>cr_m</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
   </si>
   <si>
     <t>.06</t>
   </si>
   <si>
-    <t>3.72</t>
-  </si>
-  <si>
-    <t>(4.72)</t>
-  </si>
-  <si>
-    <t>[.002739726100117, 25.51000022888184]</t>
-  </si>
-  <si>
-    <t>455.49</t>
-  </si>
-  <si>
-    <t>(656.22)</t>
-  </si>
-  <si>
-    <t>[21.42, 11284.789]</t>
-  </si>
-  <si>
-    <t>57.36</t>
-  </si>
-  <si>
-    <t>(15.57)</t>
-  </si>
-  <si>
-    <t>[7, 147]</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>At will worker</t>
-  </si>
-  <si>
-    <t>Total asked</t>
-  </si>
-  <si>
-    <t>.02</t>
-  </si>
-  <si>
-    <t>.09</t>
-  </si>
-  <si>
-    <t>(.29)</t>
-  </si>
-  <si>
-    <t>.41</t>
-  </si>
-  <si>
-    <t>.13</t>
-  </si>
-  <si>
-    <t>(.34)</t>
-  </si>
-  <si>
-    <t>58.14</t>
+    <t>(.24)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.46</t>
+  </si>
+  <si>
+    <t>(.5)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.08</t>
+  </si>
+  <si>
+    <t>(.27)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>4.33</t>
+  </si>
+  <si>
+    <t>(5.74)</t>
+  </si>
+  <si>
+    <t>[.0164383556693792, 60.60821914672852]</t>
+  </si>
+  <si>
+    <t>605.3000000000001</t>
+  </si>
+  <si>
+    <t>(1007.75)</t>
+  </si>
+  <si>
+    <t>[50, 19719.359375]</t>
+  </si>
+  <si>
+    <t>56.15</t>
+  </si>
+  <si>
+    <t>(13.38)</t>
+  </si>
+  <si>
+    <t>[6, 122.5]</t>
+  </si>
+  <si>
+    <t>win</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>liq_total</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>c_total</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>con</t>
+  </si>
+  <si>
+    <t>.42</t>
+  </si>
+  <si>
+    <t>(.49)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>cr_0</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>cr_m</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>.47</t>
+  </si>
+  <si>
+    <t>(.5)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
   </si>
   <si>
     <t>.45</t>
   </si>
   <si>
-    <t>Observations</t>
-  </si>
-  <si>
-    <t>Data: ScaleUp</t>
-  </si>
-  <si>
-    <t>Panel B: Basic Variables</t>
-  </si>
-  <si>
-    <t>.08</t>
-  </si>
-  <si>
-    <t>(.27)</t>
-  </si>
-  <si>
-    <t>HD</t>
-  </si>
-  <si>
-    <t>HD Subcourt 7</t>
-  </si>
-  <si>
-    <t>651620.37</t>
-  </si>
-  <si>
-    <t>(1501129.1)</t>
-  </si>
-  <si>
-    <t>4.82</t>
-  </si>
-  <si>
-    <t>(6.01)</t>
-  </si>
-  <si>
-    <t>[.002739726100117, 49.47123336791992]</t>
-  </si>
-  <si>
-    <t>953.12</t>
-  </si>
-  <si>
-    <t>(2498.66)</t>
-  </si>
-  <si>
-    <t>(17.06)</t>
-  </si>
-  <si>
-    <t>Tenure (years)</t>
-  </si>
-  <si>
-    <t>[40, 15157.91796875]</t>
-  </si>
-  <si>
-    <t>[2, 126]</t>
-  </si>
-  <si>
-    <t>.6800000000000001</t>
-  </si>
-  <si>
-    <t>Phase 1</t>
-  </si>
-  <si>
-    <t>Phase 2</t>
-  </si>
-  <si>
-    <t>611740.23</t>
-  </si>
-  <si>
-    <t>(3151612.79)</t>
-  </si>
-  <si>
-    <t>[7623.42138671875, 100850536]</t>
-  </si>
-  <si>
-    <t>4.05</t>
-  </si>
-  <si>
-    <t>(5.44)</t>
-  </si>
-  <si>
-    <t>[.002739726100117, 44.82191848754883]</t>
-  </si>
-  <si>
-    <t>622.39</t>
-  </si>
-  <si>
-    <t>(908.99)</t>
-  </si>
-  <si>
-    <t>56.76</t>
-  </si>
-  <si>
-    <t>(14.22)</t>
-  </si>
-  <si>
-    <t>23525.76</t>
-  </si>
-  <si>
-    <t>(54298.25)</t>
-  </si>
-  <si>
-    <t>[0, 400000]</t>
-  </si>
-  <si>
-    <t>20298.19</t>
-  </si>
-  <si>
-    <t>(46612.46)</t>
-  </si>
-  <si>
-    <t>(.14)</t>
-  </si>
-  <si>
-    <t>(.09)</t>
-  </si>
-  <si>
-    <t>(.12)</t>
-  </si>
-  <si>
-    <t>liq_total_tope</t>
-  </si>
-  <si>
-    <t>Duration (years)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Losing court ruling </t>
-  </si>
-  <si>
-    <t>Winning court ruling</t>
-  </si>
-  <si>
-    <t>cr_0</t>
-  </si>
-  <si>
-    <t>cr_m</t>
+    <t>(.5)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>3.71</t>
+  </si>
+  <si>
+    <t>(4.74)</t>
+  </si>
+  <si>
+    <t>[.0082191778346896, 41.33424758911133]</t>
+  </si>
+  <si>
+    <t>323.1</t>
+  </si>
+  <si>
+    <t>(634.99)</t>
+  </si>
+  <si>
+    <t>[36.66666793823242, 18200]</t>
+  </si>
+  <si>
+    <t>52.88</t>
+  </si>
+  <si>
+    <t>(15.52)</t>
+  </si>
+  <si>
+    <t>[0, 168]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,6 +1394,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -493,8 +1435,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -503,35 +1447,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -848,48 +1798,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:M18"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:P18"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
+    <row r="2" x14ac:dyDescent="0.35">
+      <c r="B2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="9" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+    </row>
+    <row r="3" x14ac:dyDescent="0.35">
+      <c r="B3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -921,365 +1871,437 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>405</v>
       </c>
       <c r="B5">
         <v>5005</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>231</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>233</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>322</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>324</v>
       </c>
       <c r="H5">
         <v>857</v>
       </c>
       <c r="I5" t="s">
-        <v>62</v>
+        <v>282</v>
       </c>
       <c r="J5" t="s">
-        <v>8</v>
+        <v>284</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>34</v>
+        <v>364</v>
       </c>
       <c r="M5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>366</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>406</v>
+      </c>
+      <c r="P5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>9</v>
+        <v>232</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>323</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>283</v>
       </c>
       <c r="L6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <v>365</v>
+      </c>
+      <c r="O6" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>409</v>
       </c>
       <c r="B7">
-        <v>5003</v>
+        <v>5005</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>235</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>237</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="H7">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="I7" t="s">
-        <v>126</v>
+        <v>285</v>
       </c>
       <c r="J7" t="s">
-        <v>125</v>
+        <v>287</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
+        <v>368</v>
       </c>
       <c r="M7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>370</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>410</v>
+      </c>
+      <c r="P7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>124</v>
+        <v>236</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>327</v>
       </c>
       <c r="I8" t="s">
-        <v>127</v>
+        <v>286</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>369</v>
+      </c>
+      <c r="O8" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>413</v>
       </c>
       <c r="B9">
         <v>5005</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>239</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>241</v>
       </c>
       <c r="E9">
-        <v>1108</v>
+        <v>548</v>
       </c>
       <c r="F9" t="s">
-        <v>99</v>
+        <v>330</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>332</v>
       </c>
       <c r="H9">
         <v>857</v>
       </c>
       <c r="I9" t="s">
-        <v>63</v>
+        <v>288</v>
       </c>
       <c r="J9" t="s">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="K9">
-        <v>1841</v>
+        <v>1087</v>
       </c>
       <c r="L9" t="s">
-        <v>113</v>
+        <v>372</v>
       </c>
       <c r="M9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+        <v>374</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>414</v>
+      </c>
+      <c r="P9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>45</v>
+        <v>240</v>
       </c>
       <c r="F10" t="s">
-        <v>100</v>
+        <v>331</v>
       </c>
       <c r="I10" t="s">
-        <v>64</v>
+        <v>289</v>
       </c>
       <c r="L10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+      <c r="O10" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>417</v>
       </c>
       <c r="B11">
         <v>5005</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>243</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="E11">
-        <v>3060</v>
+        <v>628</v>
       </c>
       <c r="F11" t="s">
-        <v>85</v>
+        <v>334</v>
       </c>
       <c r="G11" t="s">
-        <v>8</v>
+        <v>336</v>
       </c>
       <c r="H11">
         <v>857</v>
       </c>
       <c r="I11" t="s">
-        <v>110</v>
+        <v>291</v>
       </c>
       <c r="J11" t="s">
-        <v>8</v>
+        <v>293</v>
       </c>
       <c r="K11">
-        <v>1840</v>
+        <v>1097</v>
       </c>
       <c r="L11" t="s">
-        <v>88</v>
+        <v>376</v>
       </c>
       <c r="M11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+        <v>378</v>
+      </c>
+      <c r="N11">
+        <v>1929</v>
+      </c>
+      <c r="O11" t="s">
+        <v>418</v>
+      </c>
+      <c r="P11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="12" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>9</v>
+        <v>244</v>
       </c>
       <c r="F12" t="s">
-        <v>86</v>
+        <v>335</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>292</v>
       </c>
       <c r="L12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+        <v>377</v>
+      </c>
+      <c r="O12" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>421</v>
       </c>
       <c r="B13">
         <v>5005</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>247</v>
       </c>
       <c r="D13" t="s">
-        <v>8</v>
+        <v>249</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>338</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>340</v>
       </c>
       <c r="H13">
         <v>857</v>
       </c>
       <c r="I13" t="s">
-        <v>56</v>
+        <v>294</v>
       </c>
       <c r="J13" t="s">
-        <v>8</v>
+        <v>296</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>34</v>
+        <v>380</v>
       </c>
       <c r="M13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+        <v>382</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>422</v>
+      </c>
+      <c r="P13" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="14" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>18</v>
+        <v>248</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="I14" t="s">
-        <v>129</v>
+        <v>295</v>
       </c>
       <c r="L14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+        <v>381</v>
+      </c>
+      <c r="O14" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>425</v>
       </c>
       <c r="B15">
         <v>5005</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>251</v>
       </c>
       <c r="D15" t="s">
-        <v>8</v>
+        <v>253</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>342</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>344</v>
       </c>
       <c r="H15">
         <v>857</v>
       </c>
       <c r="I15" t="s">
-        <v>84</v>
+        <v>297</v>
       </c>
       <c r="J15" t="s">
-        <v>8</v>
+        <v>299</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>34</v>
+        <v>384</v>
       </c>
       <c r="M15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>426</v>
+      </c>
+      <c r="P15" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="16" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>128</v>
+        <v>252</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>343</v>
       </c>
       <c r="I16" t="s">
-        <v>130</v>
+        <v>298</v>
       </c>
       <c r="L16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+        <v>385</v>
+      </c>
+      <c r="O16" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="17" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>254</v>
       </c>
       <c r="B17">
         <v>5004</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>255</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>257</v>
       </c>
       <c r="H17">
         <v>856</v>
       </c>
       <c r="I17" t="s">
-        <v>28</v>
+        <v>300</v>
       </c>
       <c r="J17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="18" x14ac:dyDescent="0.35">
       <c r="C18" t="s">
-        <v>59</v>
+        <v>256</v>
       </c>
       <c r="I18" t="s">
-        <v>66</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -1296,48 +2318,53 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:M16"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:P16"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="9" t="s">
+    <row r="2" x14ac:dyDescent="0.35">
+      <c r="B2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+    </row>
+    <row r="3" x14ac:dyDescent="0.35">
+      <c r="B3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+    </row>
+    <row r="4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1369,338 +2396,411 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>258</v>
       </c>
       <c r="B5">
         <v>5001</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>261</v>
       </c>
       <c r="E5">
-        <v>1108</v>
+        <v>599</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
+        <v>345</v>
       </c>
       <c r="G5" t="s">
-        <v>8</v>
+        <v>347</v>
       </c>
       <c r="H5">
         <v>857</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>303</v>
       </c>
       <c r="J5" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="K5">
-        <v>1841</v>
+        <v>1087</v>
       </c>
       <c r="L5" t="s">
-        <v>17</v>
+        <v>387</v>
       </c>
       <c r="M5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>389</v>
+      </c>
+      <c r="N5">
+        <v>568</v>
+      </c>
+      <c r="O5" t="s">
+        <v>429</v>
+      </c>
+      <c r="P5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="6" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>12</v>
+        <v>260</v>
       </c>
       <c r="F6" t="s">
-        <v>86</v>
+        <v>346</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>304</v>
       </c>
       <c r="L6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <v>388</v>
+      </c>
+      <c r="O6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>262</v>
       </c>
       <c r="B7">
         <v>5004</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>263</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>265</v>
       </c>
       <c r="E7">
-        <v>1108</v>
+        <v>599</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>348</v>
       </c>
       <c r="G7" t="s">
-        <v>8</v>
+        <v>350</v>
       </c>
       <c r="H7">
         <v>857</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>306</v>
       </c>
       <c r="J7" t="s">
-        <v>8</v>
+        <v>308</v>
       </c>
       <c r="K7">
-        <v>1841</v>
+        <v>1087</v>
       </c>
       <c r="L7" t="s">
-        <v>91</v>
+        <v>390</v>
       </c>
       <c r="M7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>392</v>
+      </c>
+      <c r="N7">
+        <v>1927</v>
+      </c>
+      <c r="O7" t="s">
+        <v>432</v>
+      </c>
+      <c r="P7" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="8" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>15</v>
+        <v>264</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>349</v>
       </c>
       <c r="I8" t="s">
-        <v>9</v>
+        <v>307</v>
       </c>
       <c r="L8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>391</v>
+      </c>
+      <c r="O8" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>266</v>
       </c>
       <c r="B9">
         <v>4993</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>267</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>269</v>
       </c>
       <c r="E9">
-        <v>1108</v>
+        <v>599</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>351</v>
       </c>
       <c r="G9" t="s">
-        <v>8</v>
+        <v>353</v>
       </c>
       <c r="H9">
         <v>857</v>
       </c>
       <c r="I9" t="s">
-        <v>71</v>
+        <v>309</v>
       </c>
       <c r="J9" t="s">
-        <v>8</v>
+        <v>311</v>
       </c>
       <c r="K9">
-        <v>1840</v>
+        <v>1087</v>
       </c>
       <c r="L9" t="s">
-        <v>95</v>
+        <v>393</v>
       </c>
       <c r="M9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+        <v>395</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>435</v>
+      </c>
+      <c r="P9" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="10" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>18</v>
+        <v>268</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>352</v>
       </c>
       <c r="I10" t="s">
-        <v>40</v>
+        <v>310</v>
       </c>
       <c r="L10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <v>394</v>
+      </c>
+      <c r="O10" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>270</v>
       </c>
       <c r="B11">
         <v>4970</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>271</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>273</v>
       </c>
       <c r="E11">
-        <v>1087</v>
+        <v>538</v>
       </c>
       <c r="F11" t="s">
-        <v>101</v>
+        <v>354</v>
       </c>
       <c r="G11" t="s">
-        <v>103</v>
+        <v>356</v>
       </c>
       <c r="H11">
         <v>857</v>
       </c>
       <c r="I11" t="s">
-        <v>72</v>
+        <v>312</v>
       </c>
       <c r="J11" t="s">
-        <v>74</v>
+        <v>314</v>
       </c>
       <c r="K11">
-        <v>1841</v>
+        <v>1047</v>
       </c>
       <c r="L11" t="s">
-        <v>116</v>
+        <v>396</v>
       </c>
       <c r="M11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+        <v>398</v>
+      </c>
+      <c r="N11">
+        <v>1929</v>
+      </c>
+      <c r="O11" t="s">
+        <v>438</v>
+      </c>
+      <c r="P11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="12" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="F12" t="s">
-        <v>102</v>
+        <v>355</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>313</v>
       </c>
       <c r="L12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+        <v>397</v>
+      </c>
+      <c r="O12" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>274</v>
       </c>
       <c r="B13">
         <v>4984</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>275</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>277</v>
       </c>
       <c r="E13">
-        <v>1097</v>
+        <v>569</v>
       </c>
       <c r="F13" t="s">
-        <v>104</v>
+        <v>357</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>359</v>
       </c>
       <c r="H13">
         <v>857</v>
       </c>
       <c r="I13" t="s">
-        <v>75</v>
+        <v>315</v>
       </c>
       <c r="J13" t="s">
-        <v>77</v>
+        <v>317</v>
       </c>
       <c r="K13">
-        <v>1841</v>
+        <v>1073</v>
       </c>
       <c r="L13" t="s">
-        <v>119</v>
+        <v>399</v>
       </c>
       <c r="M13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+        <v>401</v>
+      </c>
+      <c r="N13">
+        <v>1929</v>
+      </c>
+      <c r="O13" t="s">
+        <v>441</v>
+      </c>
+      <c r="P13" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="14" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>32</v>
+        <v>276</v>
       </c>
       <c r="F14" t="s">
-        <v>105</v>
+        <v>358</v>
       </c>
       <c r="I14" t="s">
-        <v>76</v>
+        <v>316</v>
       </c>
       <c r="L14" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+      <c r="O14" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>278</v>
       </c>
       <c r="B15">
         <v>4922</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>279</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>281</v>
       </c>
       <c r="E15">
-        <v>1072</v>
+        <v>585</v>
       </c>
       <c r="F15" t="s">
-        <v>90</v>
+        <v>360</v>
       </c>
       <c r="G15" t="s">
-        <v>39</v>
+        <v>362</v>
       </c>
       <c r="H15">
         <v>857</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>318</v>
       </c>
       <c r="J15" t="s">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="K15">
-        <v>1825</v>
+        <v>1080</v>
       </c>
       <c r="L15" t="s">
-        <v>121</v>
+        <v>402</v>
       </c>
       <c r="M15" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <v>404</v>
+      </c>
+      <c r="N15">
+        <v>925</v>
+      </c>
+      <c r="O15" t="s">
+        <v>444</v>
+      </c>
+      <c r="P15" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="16" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>26</v>
+        <v>280</v>
       </c>
       <c r="F16" t="s">
-        <v>106</v>
+        <v>361</v>
       </c>
       <c r="I16" t="s">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="L16" t="s">
-        <v>122</v>
+        <v>403</v>
+      </c>
+      <c r="O16" t="s">
+        <v>445</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="N3:P3"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="E3:G3"/>
     <mergeCell ref="H3:J3"/>
@@ -1713,41 +2813,45 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A3:E34"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A3:F34"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="11.5546875" style="3"/>
+    <col min="1" max="16384" width="11.54296875" style="3"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="15" thickBot="true" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="str">
         <f>PanelA!A4</f>
         <v>Variable</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" ht="15" thickTop="true" x14ac:dyDescent="0.35">
+      <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="B5" s="7">
         <f>ROUND(PanelA!C5,2)</f>
@@ -1760,7 +2864,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.35">
       <c r="B6" s="7" t="str">
         <f>PanelA!C6</f>
         <v>(.48)</v>
@@ -1772,75 +2876,75 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>49</v>
+    <row r="7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="B7" s="7">
-        <f>ROUND(PanelA!C7,0)</f>
-        <v>23526</v>
+        <f>ROUND(PanelA!C7,2)</f>
+        <v>23.92</v>
       </c>
       <c r="C7" s="7">
-        <f>ROUND(PanelA!I7,0)</f>
-        <v>20298</v>
+        <f>ROUND(PanelA!I7,2)</f>
+        <v>20.36</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.35">
       <c r="B8" s="7" t="str">
         <f>PanelA!C8</f>
-        <v>(54298.25)</v>
+        <v>(56.3)</v>
       </c>
       <c r="C8" s="7" t="str">
         <f>PanelA!I8</f>
-        <v>(46612.46)</v>
+        <v>(47.49)</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>83</v>
+    <row r="9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="B9" s="7">
-        <f>ROUND(PanelA!C9,0)</f>
-        <v>343060</v>
+        <f>ROUND(PanelA!C9,2)</f>
+        <v>343.06</v>
       </c>
       <c r="C9" s="7">
-        <f>ROUND(PanelA!I9,0)</f>
-        <v>301566</v>
+        <f>ROUND(PanelA!I9,2)</f>
+        <v>301.57</v>
       </c>
       <c r="D9" s="7">
-        <f>ROUND(PanelA!F9,0)</f>
-        <v>651620</v>
+        <f>ROUND(PanelA!F9,2)</f>
+        <v>598.32000000000005</v>
       </c>
       <c r="E9" s="7">
-        <f>ROUND(PanelA!L9,0)</f>
-        <v>611740</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <f>ROUND(PanelA!L9,2)</f>
+        <v>644.05999999999995</v>
+      </c>
+    </row>
+    <row r="10" x14ac:dyDescent="0.35">
       <c r="B10" s="7" t="str">
         <f>PanelA!C10</f>
-        <v>(655168.15)</v>
+        <v>(655.17)</v>
       </c>
       <c r="C10" s="7" t="str">
         <f>PanelA!I10</f>
-        <v>(551154.03)</v>
+        <v>(551.15)</v>
       </c>
       <c r="D10" s="7" t="str">
         <f>PanelA!F10</f>
-        <v>(1501129.1)</v>
+        <v>(1438.49)</v>
       </c>
       <c r="E10" s="7" t="str">
         <f>PanelA!L10</f>
-        <v>(3151612.79)</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>(3860.99)</v>
+      </c>
+    </row>
+    <row r="11" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="B11" s="7">
         <f>ROUND(PanelA!C11,2)</f>
@@ -1848,18 +2952,18 @@
       </c>
       <c r="C11" s="7">
         <f>ROUND(PanelA!I11,2)</f>
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="D11" s="7">
         <f>ROUND(PanelA!F11,2)</f>
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="E11" s="7">
         <f>ROUND(PanelA!L11,2)</f>
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="12" x14ac:dyDescent="0.35">
       <c r="B12" s="7" t="str">
         <f>PanelA!C12</f>
         <v>(.48)</v>
@@ -1870,16 +2974,16 @@
       </c>
       <c r="D12" s="7" t="str">
         <f>PanelA!F12</f>
-        <v>(.29)</v>
+        <v>(.41)</v>
       </c>
       <c r="E12" s="7" t="str">
         <f>PanelA!L12</f>
-        <v>(.34)</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>(.4)</v>
+      </c>
+    </row>
+    <row r="13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="B13" s="7">
         <f>ROUND(PanelA!C13,2)</f>
@@ -1892,21 +2996,21 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.35">
       <c r="B14" s="7" t="str">
         <f>PanelA!C14</f>
         <v>(.25)</v>
       </c>
       <c r="C14" s="7" t="str">
         <f>PanelA!I14</f>
-        <v>(.09)</v>
+        <v>(.1)</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="B15" s="7">
         <f>ROUND(PanelA!C15,2)</f>
@@ -1919,7 +3023,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.35">
       <c r="B16" s="7" t="str">
         <f>PanelA!C16</f>
         <v>(.14)</v>
@@ -1931,9 +3035,9 @@
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="B17" s="7">
         <f>ROUND(PanelA!C17,2)</f>
@@ -1946,7 +3050,7 @@
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" ht="15" thickBot="true" x14ac:dyDescent="0.4">
       <c r="B18" s="7" t="str">
         <f>PanelA!C18</f>
         <v>(.96)</v>
@@ -1958,17 +3062,18 @@
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
     </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="11" t="s">
+    <row r="19" ht="15" thickTop="true" x14ac:dyDescent="0.35">
+      <c r="B19" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-    </row>
-    <row r="20" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+    </row>
+    <row r="20" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="B20" s="7">
         <f>ROUND(PanelB!C5,2)</f>
@@ -1980,14 +3085,15 @@
       </c>
       <c r="D20" s="7">
         <f>ROUND(PanelB!F5,2)</f>
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="E20" s="7">
         <f>ROUND(PanelB!L5,2)</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.06</v>
+      </c>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" x14ac:dyDescent="0.35">
       <c r="B21" s="7" t="str">
         <f>PanelB!C6</f>
         <v>(.3)</v>
@@ -1998,16 +3104,17 @@
       </c>
       <c r="D21" s="7" t="str">
         <f>PanelB!F6</f>
-        <v>(.29)</v>
+        <v>(.32)</v>
       </c>
       <c r="E21" s="7" t="str">
         <f>PanelB!L6</f>
-        <v>(.25)</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>(.24)</v>
+      </c>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="B22" s="7">
         <f>ROUND(PanelB!C7,2)</f>
@@ -2019,14 +3126,18 @@
       </c>
       <c r="D22" s="7">
         <f>ROUND(PanelB!F7,2)</f>
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="E22" s="7">
         <f>ROUND(PanelB!L7,2)</f>
+        <v>0.46</v>
+      </c>
+      <c r="F22" s="7">
+        <f>ROUND(PanelB!O7,2)</f>
         <v>0.45</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" x14ac:dyDescent="0.35">
       <c r="B23" s="7" t="str">
         <f>PanelB!C8</f>
         <v>(.5)</v>
@@ -2043,10 +3154,14 @@
         <f>PanelB!L8</f>
         <v>(.5)</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23" s="7" t="str">
+        <f>PanelB!O8</f>
+        <v>(.5)</v>
+      </c>
+    </row>
+    <row r="24" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="B24" s="7">
         <f>ROUND(PanelB!C9,2)</f>
@@ -2058,14 +3173,15 @@
       </c>
       <c r="D24" s="7">
         <f>ROUND(PanelB!F9,2)</f>
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="E24" s="7">
         <f>ROUND(PanelB!L9,2)</f>
         <v>0.08</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" x14ac:dyDescent="0.35">
       <c r="B25" s="7" t="str">
         <f>PanelB!C10</f>
         <v>(.25)</v>
@@ -2076,16 +3192,17 @@
       </c>
       <c r="D25" s="7" t="str">
         <f>PanelB!F10</f>
-        <v>(.34)</v>
+        <v>(.39)</v>
       </c>
       <c r="E25" s="7" t="str">
         <f>PanelB!L10</f>
         <v>(.27)</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="B26" s="7">
         <f>ROUND(PanelB!C11,2)</f>
@@ -2097,14 +3214,18 @@
       </c>
       <c r="D26" s="7">
         <f>ROUND(PanelB!F11,2)</f>
-        <v>4.82</v>
+        <v>4.71</v>
       </c>
       <c r="E26" s="7">
         <f>ROUND(PanelB!L11,2)</f>
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4.33</v>
+      </c>
+      <c r="F26" s="7">
+        <f>ROUND(PanelB!O11,2)</f>
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="27" x14ac:dyDescent="0.35">
       <c r="B27" s="7" t="str">
         <f>PanelB!C12</f>
         <v>(4.99)</v>
@@ -2115,16 +3236,20 @@
       </c>
       <c r="D27" s="7" t="str">
         <f>PanelB!F12</f>
-        <v>(6.01)</v>
+        <v>(6)</v>
       </c>
       <c r="E27" s="7" t="str">
         <f>PanelB!L12</f>
-        <v>(5.44)</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <v>(5.74)</v>
+      </c>
+      <c r="F27" s="7" t="str">
+        <f>PanelB!O12</f>
+        <v>(4.74)</v>
+      </c>
+    </row>
+    <row r="28" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="B28" s="7">
         <f>ROUND(PanelB!C13,0)</f>
@@ -2136,14 +3261,18 @@
       </c>
       <c r="D28" s="7">
         <f>ROUND(PanelB!F13,0)</f>
-        <v>953</v>
+        <v>740</v>
       </c>
       <c r="E28" s="7">
         <f>ROUND(PanelB!L13,0)</f>
-        <v>622</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+        <v>605</v>
+      </c>
+      <c r="F28" s="7">
+        <f>ROUND(PanelB!O13,0)</f>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="29" x14ac:dyDescent="0.35">
       <c r="B29" s="7" t="str">
         <f>PanelB!C14</f>
         <v>(1100.8)</v>
@@ -2154,16 +3283,20 @@
       </c>
       <c r="D29" s="7" t="str">
         <f>PanelB!F14</f>
-        <v>(2498.66)</v>
+        <v>(1360.94)</v>
       </c>
       <c r="E29" s="7" t="str">
         <f>PanelB!L14</f>
-        <v>(908.99)</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+        <v>(1007.75)</v>
+      </c>
+      <c r="F29" s="7" t="str">
+        <f>PanelB!O14</f>
+        <v>(634.99)</v>
+      </c>
+    </row>
+    <row r="30" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="B30" s="7">
         <f>ROUND(PanelB!C15,2)</f>
@@ -2175,14 +3308,18 @@
       </c>
       <c r="D30" s="7">
         <f>ROUND(PanelB!F15,2)</f>
-        <v>58.14</v>
+        <v>57.31</v>
       </c>
       <c r="E30" s="7">
         <f>ROUND(PanelB!L15,2)</f>
-        <v>56.76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+        <v>56.15</v>
+      </c>
+      <c r="F30" s="7">
+        <f>ROUND(PanelB!O15,2)</f>
+        <v>52.88</v>
+      </c>
+    </row>
+    <row r="31" x14ac:dyDescent="0.35">
       <c r="B31" s="7" t="str">
         <f>PanelB!C16</f>
         <v>(15.47)</v>
@@ -2193,22 +3330,26 @@
       </c>
       <c r="D31" s="7" t="str">
         <f>PanelB!F16</f>
-        <v>(17.06)</v>
+        <v>(16.82)</v>
       </c>
       <c r="E31" s="7" t="str">
         <f>PanelB!L16</f>
-        <v>(14.22)</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+        <v>(13.38)</v>
+      </c>
+      <c r="F31" s="7" t="str">
+        <f>PanelB!O16</f>
+        <v>(15.52)</v>
+      </c>
+    </row>
+    <row r="32" x14ac:dyDescent="0.35">
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
     </row>
-    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" ht="15" thickBot="true" x14ac:dyDescent="0.4">
       <c r="A33" s="5" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="B33" s="6">
         <f>ROUND(AVERAGE(PanelA!B5:B17),0)</f>
@@ -2219,20 +3360,25 @@
         <v>857</v>
       </c>
       <c r="D33" s="6">
-        <f>ROUND(AVERAGE(PanelB!E5:E15),0)</f>
-        <v>1097</v>
+        <f>ROUND(MAX(PanelB!E5:E15),0)</f>
+        <v>599</v>
       </c>
       <c r="E33" s="6">
-        <f>ROUND(AVERAGE(PanelB!K5:K15),0)</f>
-        <v>1838</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+        <f>ROUND(MAX(PanelB!K5:K15),0)</f>
+        <v>1087</v>
+      </c>
+      <c r="F33" s="9">
+        <f>ROUND(MAX(PanelB!N5:N15),0)</f>
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="34" ht="15" thickTop="true" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B4:F4"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/paper/Tables/SS.xlsx
+++ b/paper/Tables/SS.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="664">
   <si>
     <t>Obs</t>
   </si>
@@ -1122,6 +1122,657 @@
   </si>
   <si>
     <t>(16.82)</t>
+  </si>
+  <si>
+    <t>[7, 258]</t>
+  </si>
+  <si>
+    <t>win</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>liq_total_tope</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>c_total</t>
+  </si>
+  <si>
+    <t>644.0600000000001</t>
+  </si>
+  <si>
+    <t>(3860.99)</t>
+  </si>
+  <si>
+    <t>[0, 100850.5390625]</t>
+  </si>
+  <si>
+    <t>con</t>
+  </si>
+  <si>
+    <t>.2</t>
+  </si>
+  <si>
+    <t>(.4)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>cr_0</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>cr_m</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>.06</t>
+  </si>
+  <si>
+    <t>(.24)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.46</t>
+  </si>
+  <si>
+    <t>(.5)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.08</t>
+  </si>
+  <si>
+    <t>(.27)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>4.33</t>
+  </si>
+  <si>
+    <t>(5.74)</t>
+  </si>
+  <si>
+    <t>[.0164383556693792, 60.60821914672852]</t>
+  </si>
+  <si>
+    <t>605.3000000000001</t>
+  </si>
+  <si>
+    <t>(1007.75)</t>
+  </si>
+  <si>
+    <t>[50, 19719.359375]</t>
+  </si>
+  <si>
+    <t>56.15</t>
+  </si>
+  <si>
+    <t>(13.38)</t>
+  </si>
+  <si>
+    <t>[6, 122.5]</t>
+  </si>
+  <si>
+    <t>win</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>liq_total</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>c_total</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>con</t>
+  </si>
+  <si>
+    <t>.42</t>
+  </si>
+  <si>
+    <t>(.49)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>cr_0</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>cr_m</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>.47</t>
+  </si>
+  <si>
+    <t>(.5)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.45</t>
+  </si>
+  <si>
+    <t>(.5)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>3.71</t>
+  </si>
+  <si>
+    <t>(4.74)</t>
+  </si>
+  <si>
+    <t>[.0082191778346896, 41.33424758911133]</t>
+  </si>
+  <si>
+    <t>323.1</t>
+  </si>
+  <si>
+    <t>(634.99)</t>
+  </si>
+  <si>
+    <t>[36.66666793823242, 18200]</t>
+  </si>
+  <si>
+    <t>52.88</t>
+  </si>
+  <si>
+    <t>(15.52)</t>
+  </si>
+  <si>
+    <t>[0, 168]</t>
+  </si>
+  <si>
+    <t>win</t>
+  </si>
+  <si>
+    <t>.65</t>
+  </si>
+  <si>
+    <t>(.48)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>liq_total</t>
+  </si>
+  <si>
+    <t>23.92</t>
+  </si>
+  <si>
+    <t>(56.3)</t>
+  </si>
+  <si>
+    <t>[0, 422.9779968261719]</t>
+  </si>
+  <si>
+    <t>c_total</t>
+  </si>
+  <si>
+    <t>343.06</t>
+  </si>
+  <si>
+    <t>(655.17)</t>
+  </si>
+  <si>
+    <t>[0, 4488.7158203125]</t>
+  </si>
+  <si>
+    <t>con</t>
+  </si>
+  <si>
+    <t>.63</t>
+  </si>
+  <si>
+    <t>(.48)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>cr_0</t>
+  </si>
+  <si>
+    <t>.07</t>
+  </si>
+  <si>
+    <t>(.25)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>cr_m</t>
+  </si>
+  <si>
+    <t>.02</t>
+  </si>
+  <si>
+    <t>(.14)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>duracion</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
+    <t>(.96)</t>
+  </si>
+  <si>
+    <t>[.0054794522002339, 4.960000038146973]</t>
+  </si>
+  <si>
+    <t>abogado_pub</t>
+  </si>
+  <si>
+    <t>.1</t>
+  </si>
+  <si>
+    <t>(.3)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>gen</t>
+  </si>
+  <si>
+    <t>.48</t>
+  </si>
+  <si>
+    <t>(.5)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>trabajador_base</t>
+  </si>
+  <si>
+    <t>.07</t>
+  </si>
+  <si>
+    <t>(.25)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>c_antiguedad</t>
+  </si>
+  <si>
+    <t>4.17</t>
+  </si>
+  <si>
+    <t>(4.99)</t>
+  </si>
+  <si>
+    <t>[0, 25.51000022888184]</t>
+  </si>
+  <si>
+    <t>salario_diario</t>
+  </si>
+  <si>
+    <t>470.05</t>
+  </si>
+  <si>
+    <t>(1100.8)</t>
+  </si>
+  <si>
+    <t>[3.33, 47526.54]</t>
+  </si>
+  <si>
+    <t>horas_sem</t>
+  </si>
+  <si>
+    <t>57.33</t>
+  </si>
+  <si>
+    <t>(15.47)</t>
+  </si>
+  <si>
+    <t>[3, 147]</t>
+  </si>
+  <si>
+    <t>.6900000000000001</t>
+  </si>
+  <si>
+    <t>(.46)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>20.36</t>
+  </si>
+  <si>
+    <t>(47.49)</t>
+  </si>
+  <si>
+    <t>[0, 422.9779968261719]</t>
+  </si>
+  <si>
+    <t>301.57</t>
+  </si>
+  <si>
+    <t>(551.15)</t>
+  </si>
+  <si>
+    <t>[6.805358409881592, 4488.7158203125]</t>
+  </si>
+  <si>
+    <t>.67</t>
+  </si>
+  <si>
+    <t>(.47)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.01</t>
+  </si>
+  <si>
+    <t>(.1)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.02</t>
+  </si>
+  <si>
+    <t>(.12)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.98</t>
+  </si>
+  <si>
+    <t>(.71)</t>
+  </si>
+  <si>
+    <t>[.0054794522002339, 4.290410995483398]</t>
+  </si>
+  <si>
+    <t>.15</t>
+  </si>
+  <si>
+    <t>(.36)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.35</t>
+  </si>
+  <si>
+    <t>(.48)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.06</t>
+  </si>
+  <si>
+    <t>(.23)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>3.72</t>
+  </si>
+  <si>
+    <t>(4.72)</t>
+  </si>
+  <si>
+    <t>[.002739726100117, 25.51000022888184]</t>
+  </si>
+  <si>
+    <t>455.49</t>
+  </si>
+  <si>
+    <t>(656.22)</t>
+  </si>
+  <si>
+    <t>[21.42, 11284.789]</t>
+  </si>
+  <si>
+    <t>57.36</t>
+  </si>
+  <si>
+    <t>(15.57)</t>
+  </si>
+  <si>
+    <t>[7, 147]</t>
+  </si>
+  <si>
+    <t>win</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>liq_total</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>c_total</t>
+  </si>
+  <si>
+    <t>598.3200000000001</t>
+  </si>
+  <si>
+    <t>(1438.49)</t>
+  </si>
+  <si>
+    <t>[0, 18704.697265625]</t>
+  </si>
+  <si>
+    <t>con</t>
+  </si>
+  <si>
+    <t>.22</t>
+  </si>
+  <si>
+    <t>(.41)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>cr_0</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>cr_m</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(.)</t>
+  </si>
+  <si>
+    <t>[, ]</t>
+  </si>
+  <si>
+    <t>.11</t>
+  </si>
+  <si>
+    <t>(.32)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.42</t>
+  </si>
+  <si>
+    <t>(.49)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>.18</t>
+  </si>
+  <si>
+    <t>(.39)</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>4.71</t>
+  </si>
+  <si>
+    <t>(6)</t>
+  </si>
+  <si>
+    <t>[.0219178088009357, 49.47123336791992]</t>
+  </si>
+  <si>
+    <t>739.91</t>
+  </si>
+  <si>
+    <t>(1360.9)</t>
+  </si>
+  <si>
+    <t>[30, 16080.0153333333]</t>
+  </si>
+  <si>
+    <t>57.33</t>
+  </si>
+  <si>
+    <t>(16.83)</t>
   </si>
   <si>
     <t>[7, 258]</t>
@@ -1873,435 +2524,435 @@
     </row>
     <row r="5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>405</v>
+        <v>622</v>
       </c>
       <c r="B5">
         <v>5005</v>
       </c>
       <c r="C5" t="s">
-        <v>231</v>
+        <v>448</v>
       </c>
       <c r="D5" t="s">
-        <v>233</v>
+        <v>450</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>322</v>
+        <v>539</v>
       </c>
       <c r="G5" t="s">
-        <v>324</v>
+        <v>541</v>
       </c>
       <c r="H5">
         <v>857</v>
       </c>
       <c r="I5" t="s">
-        <v>282</v>
+        <v>499</v>
       </c>
       <c r="J5" t="s">
-        <v>284</v>
+        <v>501</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>364</v>
+        <v>581</v>
       </c>
       <c r="M5" t="s">
-        <v>366</v>
+        <v>583</v>
       </c>
       <c r="N5">
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>406</v>
+        <v>623</v>
       </c>
       <c r="P5" t="s">
-        <v>408</v>
+        <v>625</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>232</v>
+        <v>449</v>
       </c>
       <c r="F6" t="s">
-        <v>323</v>
+        <v>540</v>
       </c>
       <c r="I6" t="s">
-        <v>283</v>
+        <v>500</v>
       </c>
       <c r="L6" t="s">
-        <v>365</v>
+        <v>582</v>
       </c>
       <c r="O6" t="s">
-        <v>407</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>409</v>
+        <v>626</v>
       </c>
       <c r="B7">
         <v>5005</v>
       </c>
       <c r="C7" t="s">
-        <v>235</v>
+        <v>452</v>
       </c>
       <c r="D7" t="s">
-        <v>237</v>
+        <v>454</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>326</v>
+        <v>543</v>
       </c>
       <c r="G7" t="s">
-        <v>328</v>
+        <v>545</v>
       </c>
       <c r="H7">
         <v>857</v>
       </c>
       <c r="I7" t="s">
-        <v>285</v>
+        <v>502</v>
       </c>
       <c r="J7" t="s">
-        <v>287</v>
+        <v>504</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>368</v>
+        <v>585</v>
       </c>
       <c r="M7" t="s">
-        <v>370</v>
+        <v>587</v>
       </c>
       <c r="N7">
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>410</v>
+        <v>627</v>
       </c>
       <c r="P7" t="s">
-        <v>412</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>236</v>
+        <v>453</v>
       </c>
       <c r="F8" t="s">
-        <v>327</v>
+        <v>544</v>
       </c>
       <c r="I8" t="s">
-        <v>286</v>
+        <v>503</v>
       </c>
       <c r="L8" t="s">
-        <v>369</v>
+        <v>586</v>
       </c>
       <c r="O8" t="s">
-        <v>411</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>413</v>
+        <v>630</v>
       </c>
       <c r="B9">
         <v>5005</v>
       </c>
       <c r="C9" t="s">
-        <v>239</v>
+        <v>456</v>
       </c>
       <c r="D9" t="s">
-        <v>241</v>
+        <v>458</v>
       </c>
       <c r="E9">
         <v>548</v>
       </c>
       <c r="F9" t="s">
-        <v>330</v>
+        <v>547</v>
       </c>
       <c r="G9" t="s">
-        <v>332</v>
+        <v>549</v>
       </c>
       <c r="H9">
         <v>857</v>
       </c>
       <c r="I9" t="s">
-        <v>288</v>
+        <v>505</v>
       </c>
       <c r="J9" t="s">
-        <v>290</v>
+        <v>507</v>
       </c>
       <c r="K9">
         <v>1087</v>
       </c>
       <c r="L9" t="s">
-        <v>372</v>
+        <v>589</v>
       </c>
       <c r="M9" t="s">
-        <v>374</v>
+        <v>591</v>
       </c>
       <c r="N9">
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>414</v>
+        <v>631</v>
       </c>
       <c r="P9" t="s">
-        <v>416</v>
+        <v>633</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>240</v>
+        <v>457</v>
       </c>
       <c r="F10" t="s">
-        <v>331</v>
+        <v>548</v>
       </c>
       <c r="I10" t="s">
-        <v>289</v>
+        <v>506</v>
       </c>
       <c r="L10" t="s">
-        <v>373</v>
+        <v>590</v>
       </c>
       <c r="O10" t="s">
-        <v>415</v>
+        <v>632</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>417</v>
+        <v>634</v>
       </c>
       <c r="B11">
         <v>5005</v>
       </c>
       <c r="C11" t="s">
-        <v>243</v>
+        <v>460</v>
       </c>
       <c r="D11" t="s">
-        <v>245</v>
+        <v>462</v>
       </c>
       <c r="E11">
         <v>628</v>
       </c>
       <c r="F11" t="s">
-        <v>334</v>
+        <v>551</v>
       </c>
       <c r="G11" t="s">
-        <v>336</v>
+        <v>553</v>
       </c>
       <c r="H11">
         <v>857</v>
       </c>
       <c r="I11" t="s">
-        <v>291</v>
+        <v>508</v>
       </c>
       <c r="J11" t="s">
-        <v>293</v>
+        <v>510</v>
       </c>
       <c r="K11">
         <v>1097</v>
       </c>
       <c r="L11" t="s">
-        <v>376</v>
+        <v>593</v>
       </c>
       <c r="M11" t="s">
-        <v>378</v>
+        <v>595</v>
       </c>
       <c r="N11">
         <v>1929</v>
       </c>
       <c r="O11" t="s">
-        <v>418</v>
+        <v>635</v>
       </c>
       <c r="P11" t="s">
-        <v>420</v>
+        <v>637</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>244</v>
+        <v>461</v>
       </c>
       <c r="F12" t="s">
-        <v>335</v>
+        <v>552</v>
       </c>
       <c r="I12" t="s">
-        <v>292</v>
+        <v>509</v>
       </c>
       <c r="L12" t="s">
-        <v>377</v>
+        <v>594</v>
       </c>
       <c r="O12" t="s">
-        <v>419</v>
+        <v>636</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>421</v>
+        <v>638</v>
       </c>
       <c r="B13">
         <v>5005</v>
       </c>
       <c r="C13" t="s">
-        <v>247</v>
+        <v>464</v>
       </c>
       <c r="D13" t="s">
-        <v>249</v>
+        <v>466</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>338</v>
+        <v>555</v>
       </c>
       <c r="G13" t="s">
-        <v>340</v>
+        <v>557</v>
       </c>
       <c r="H13">
         <v>857</v>
       </c>
       <c r="I13" t="s">
-        <v>294</v>
+        <v>511</v>
       </c>
       <c r="J13" t="s">
-        <v>296</v>
+        <v>513</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>380</v>
+        <v>597</v>
       </c>
       <c r="M13" t="s">
-        <v>382</v>
+        <v>599</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>422</v>
+        <v>639</v>
       </c>
       <c r="P13" t="s">
-        <v>424</v>
+        <v>641</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>248</v>
+        <v>465</v>
       </c>
       <c r="F14" t="s">
-        <v>339</v>
+        <v>556</v>
       </c>
       <c r="I14" t="s">
-        <v>295</v>
+        <v>512</v>
       </c>
       <c r="L14" t="s">
-        <v>381</v>
+        <v>598</v>
       </c>
       <c r="O14" t="s">
-        <v>423</v>
+        <v>640</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>425</v>
+        <v>642</v>
       </c>
       <c r="B15">
         <v>5005</v>
       </c>
       <c r="C15" t="s">
-        <v>251</v>
+        <v>468</v>
       </c>
       <c r="D15" t="s">
-        <v>253</v>
+        <v>470</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>342</v>
+        <v>559</v>
       </c>
       <c r="G15" t="s">
-        <v>344</v>
+        <v>561</v>
       </c>
       <c r="H15">
         <v>857</v>
       </c>
       <c r="I15" t="s">
-        <v>297</v>
+        <v>514</v>
       </c>
       <c r="J15" t="s">
-        <v>299</v>
+        <v>516</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>384</v>
+        <v>601</v>
       </c>
       <c r="M15" t="s">
-        <v>386</v>
+        <v>603</v>
       </c>
       <c r="N15">
         <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>426</v>
+        <v>643</v>
       </c>
       <c r="P15" t="s">
-        <v>428</v>
+        <v>645</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>252</v>
+        <v>469</v>
       </c>
       <c r="F16" t="s">
-        <v>343</v>
+        <v>560</v>
       </c>
       <c r="I16" t="s">
-        <v>298</v>
+        <v>515</v>
       </c>
       <c r="L16" t="s">
-        <v>385</v>
+        <v>602</v>
       </c>
       <c r="O16" t="s">
-        <v>427</v>
+        <v>644</v>
       </c>
     </row>
     <row r="17" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>254</v>
+        <v>471</v>
       </c>
       <c r="B17">
         <v>5004</v>
       </c>
       <c r="C17" t="s">
-        <v>255</v>
+        <v>472</v>
       </c>
       <c r="D17" t="s">
-        <v>257</v>
+        <v>474</v>
       </c>
       <c r="H17">
         <v>856</v>
       </c>
       <c r="I17" t="s">
-        <v>300</v>
+        <v>517</v>
       </c>
       <c r="J17" t="s">
-        <v>302</v>
+        <v>519</v>
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.35">
       <c r="C18" t="s">
-        <v>256</v>
+        <v>473</v>
       </c>
       <c r="I18" t="s">
-        <v>301</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -2398,404 +3049,404 @@
     </row>
     <row r="5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>258</v>
+        <v>475</v>
       </c>
       <c r="B5">
         <v>5001</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>476</v>
       </c>
       <c r="D5" t="s">
-        <v>261</v>
+        <v>478</v>
       </c>
       <c r="E5">
         <v>599</v>
       </c>
       <c r="F5" t="s">
-        <v>345</v>
+        <v>562</v>
       </c>
       <c r="G5" t="s">
-        <v>347</v>
+        <v>564</v>
       </c>
       <c r="H5">
         <v>857</v>
       </c>
       <c r="I5" t="s">
-        <v>303</v>
+        <v>520</v>
       </c>
       <c r="J5" t="s">
-        <v>305</v>
+        <v>522</v>
       </c>
       <c r="K5">
         <v>1087</v>
       </c>
       <c r="L5" t="s">
-        <v>387</v>
+        <v>604</v>
       </c>
       <c r="M5" t="s">
-        <v>389</v>
+        <v>606</v>
       </c>
       <c r="N5">
         <v>568</v>
       </c>
       <c r="O5" t="s">
-        <v>429</v>
+        <v>646</v>
       </c>
       <c r="P5" t="s">
-        <v>431</v>
+        <v>648</v>
       </c>
     </row>
     <row r="6" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>260</v>
+        <v>477</v>
       </c>
       <c r="F6" t="s">
-        <v>346</v>
+        <v>563</v>
       </c>
       <c r="I6" t="s">
-        <v>304</v>
+        <v>521</v>
       </c>
       <c r="L6" t="s">
-        <v>388</v>
+        <v>605</v>
       </c>
       <c r="O6" t="s">
-        <v>430</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>262</v>
+        <v>479</v>
       </c>
       <c r="B7">
         <v>5004</v>
       </c>
       <c r="C7" t="s">
-        <v>263</v>
+        <v>480</v>
       </c>
       <c r="D7" t="s">
-        <v>265</v>
+        <v>482</v>
       </c>
       <c r="E7">
         <v>599</v>
       </c>
       <c r="F7" t="s">
-        <v>348</v>
+        <v>565</v>
       </c>
       <c r="G7" t="s">
-        <v>350</v>
+        <v>567</v>
       </c>
       <c r="H7">
         <v>857</v>
       </c>
       <c r="I7" t="s">
-        <v>306</v>
+        <v>523</v>
       </c>
       <c r="J7" t="s">
-        <v>308</v>
+        <v>525</v>
       </c>
       <c r="K7">
         <v>1087</v>
       </c>
       <c r="L7" t="s">
-        <v>390</v>
+        <v>607</v>
       </c>
       <c r="M7" t="s">
-        <v>392</v>
+        <v>609</v>
       </c>
       <c r="N7">
         <v>1927</v>
       </c>
       <c r="O7" t="s">
-        <v>432</v>
+        <v>649</v>
       </c>
       <c r="P7" t="s">
-        <v>434</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>264</v>
+        <v>481</v>
       </c>
       <c r="F8" t="s">
-        <v>349</v>
+        <v>566</v>
       </c>
       <c r="I8" t="s">
-        <v>307</v>
+        <v>524</v>
       </c>
       <c r="L8" t="s">
-        <v>391</v>
+        <v>608</v>
       </c>
       <c r="O8" t="s">
-        <v>433</v>
+        <v>650</v>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>266</v>
+        <v>483</v>
       </c>
       <c r="B9">
         <v>4993</v>
       </c>
       <c r="C9" t="s">
-        <v>267</v>
+        <v>484</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>486</v>
       </c>
       <c r="E9">
         <v>599</v>
       </c>
       <c r="F9" t="s">
-        <v>351</v>
+        <v>568</v>
       </c>
       <c r="G9" t="s">
-        <v>353</v>
+        <v>570</v>
       </c>
       <c r="H9">
         <v>857</v>
       </c>
       <c r="I9" t="s">
-        <v>309</v>
+        <v>526</v>
       </c>
       <c r="J9" t="s">
-        <v>311</v>
+        <v>528</v>
       </c>
       <c r="K9">
         <v>1087</v>
       </c>
       <c r="L9" t="s">
-        <v>393</v>
+        <v>610</v>
       </c>
       <c r="M9" t="s">
-        <v>395</v>
+        <v>612</v>
       </c>
       <c r="N9">
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>435</v>
+        <v>652</v>
       </c>
       <c r="P9" t="s">
-        <v>437</v>
+        <v>654</v>
       </c>
     </row>
     <row r="10" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>268</v>
+        <v>485</v>
       </c>
       <c r="F10" t="s">
-        <v>352</v>
+        <v>569</v>
       </c>
       <c r="I10" t="s">
-        <v>310</v>
+        <v>527</v>
       </c>
       <c r="L10" t="s">
-        <v>394</v>
+        <v>611</v>
       </c>
       <c r="O10" t="s">
-        <v>436</v>
+        <v>653</v>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>270</v>
+        <v>487</v>
       </c>
       <c r="B11">
         <v>4970</v>
       </c>
       <c r="C11" t="s">
-        <v>271</v>
+        <v>488</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>490</v>
       </c>
       <c r="E11">
         <v>538</v>
       </c>
       <c r="F11" t="s">
-        <v>354</v>
+        <v>571</v>
       </c>
       <c r="G11" t="s">
-        <v>356</v>
+        <v>573</v>
       </c>
       <c r="H11">
         <v>857</v>
       </c>
       <c r="I11" t="s">
-        <v>312</v>
+        <v>529</v>
       </c>
       <c r="J11" t="s">
-        <v>314</v>
+        <v>531</v>
       </c>
       <c r="K11">
         <v>1047</v>
       </c>
       <c r="L11" t="s">
-        <v>396</v>
+        <v>613</v>
       </c>
       <c r="M11" t="s">
-        <v>398</v>
+        <v>615</v>
       </c>
       <c r="N11">
         <v>1929</v>
       </c>
       <c r="O11" t="s">
-        <v>438</v>
+        <v>655</v>
       </c>
       <c r="P11" t="s">
-        <v>440</v>
+        <v>657</v>
       </c>
     </row>
     <row r="12" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>272</v>
+        <v>489</v>
       </c>
       <c r="F12" t="s">
-        <v>355</v>
+        <v>572</v>
       </c>
       <c r="I12" t="s">
-        <v>313</v>
+        <v>530</v>
       </c>
       <c r="L12" t="s">
-        <v>397</v>
+        <v>614</v>
       </c>
       <c r="O12" t="s">
-        <v>439</v>
+        <v>656</v>
       </c>
     </row>
     <row r="13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>274</v>
+        <v>491</v>
       </c>
       <c r="B13">
         <v>4984</v>
       </c>
       <c r="C13" t="s">
-        <v>275</v>
+        <v>492</v>
       </c>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>494</v>
       </c>
       <c r="E13">
         <v>569</v>
       </c>
       <c r="F13" t="s">
-        <v>357</v>
+        <v>574</v>
       </c>
       <c r="G13" t="s">
-        <v>359</v>
+        <v>576</v>
       </c>
       <c r="H13">
         <v>857</v>
       </c>
       <c r="I13" t="s">
-        <v>315</v>
+        <v>532</v>
       </c>
       <c r="J13" t="s">
-        <v>317</v>
+        <v>534</v>
       </c>
       <c r="K13">
         <v>1073</v>
       </c>
       <c r="L13" t="s">
-        <v>399</v>
+        <v>616</v>
       </c>
       <c r="M13" t="s">
-        <v>401</v>
+        <v>618</v>
       </c>
       <c r="N13">
         <v>1929</v>
       </c>
       <c r="O13" t="s">
-        <v>441</v>
+        <v>658</v>
       </c>
       <c r="P13" t="s">
-        <v>443</v>
+        <v>660</v>
       </c>
     </row>
     <row r="14" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>276</v>
+        <v>493</v>
       </c>
       <c r="F14" t="s">
-        <v>358</v>
+        <v>575</v>
       </c>
       <c r="I14" t="s">
-        <v>316</v>
+        <v>533</v>
       </c>
       <c r="L14" t="s">
-        <v>400</v>
+        <v>617</v>
       </c>
       <c r="O14" t="s">
-        <v>442</v>
+        <v>659</v>
       </c>
     </row>
     <row r="15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>278</v>
+        <v>495</v>
       </c>
       <c r="B15">
         <v>4922</v>
       </c>
       <c r="C15" t="s">
-        <v>279</v>
+        <v>496</v>
       </c>
       <c r="D15" t="s">
-        <v>281</v>
+        <v>498</v>
       </c>
       <c r="E15">
         <v>585</v>
       </c>
       <c r="F15" t="s">
-        <v>360</v>
+        <v>577</v>
       </c>
       <c r="G15" t="s">
-        <v>362</v>
+        <v>579</v>
       </c>
       <c r="H15">
         <v>857</v>
       </c>
       <c r="I15" t="s">
-        <v>318</v>
+        <v>535</v>
       </c>
       <c r="J15" t="s">
-        <v>320</v>
+        <v>537</v>
       </c>
       <c r="K15">
         <v>1080</v>
       </c>
       <c r="L15" t="s">
-        <v>402</v>
+        <v>619</v>
       </c>
       <c r="M15" t="s">
-        <v>404</v>
+        <v>621</v>
       </c>
       <c r="N15">
         <v>925</v>
       </c>
       <c r="O15" t="s">
-        <v>444</v>
+        <v>661</v>
       </c>
       <c r="P15" t="s">
-        <v>446</v>
+        <v>663</v>
       </c>
     </row>
     <row r="16" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>280</v>
+        <v>497</v>
       </c>
       <c r="F16" t="s">
-        <v>361</v>
+        <v>578</v>
       </c>
       <c r="I16" t="s">
-        <v>319</v>
+        <v>536</v>
       </c>
       <c r="L16" t="s">
-        <v>403</v>
+        <v>620</v>
       </c>
       <c r="O16" t="s">
-        <v>445</v>
+        <v>662</v>
       </c>
     </row>
   </sheetData>
